--- a/UC-2.xlsx
+++ b/UC-2.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Library/Mobile Documents/com~apple~CloudDocs/A-Uni/Year 3/Sem 2/G7 Code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Documents/GitHub/g6-analysis-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C38328-40FF-0F41-BB07-8170B83CA3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC9A519-2414-9641-BEFF-8533E2FAB906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Structural Steel Section Proper" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Designation</t>
   </si>
@@ -170,19 +173,34 @@
     <t>Area (mm2)</t>
   </si>
   <si>
-    <t>152x152x44</t>
-  </si>
-  <si>
-    <t>152x152x51</t>
-  </si>
-  <si>
-    <t>203x203x100</t>
-  </si>
-  <si>
-    <t>203x203x113</t>
-  </si>
-  <si>
-    <t>203x203x127</t>
+    <t>Web tw​ (mm)</t>
+  </si>
+  <si>
+    <t>Depth (h) mm</t>
+  </si>
+  <si>
+    <t>Flange tf (mm)</t>
+  </si>
+  <si>
+    <t>Root radius mm</t>
+  </si>
+  <si>
+    <t>b (mm)</t>
+  </si>
+  <si>
+    <t>203x203x127+</t>
+  </si>
+  <si>
+    <t>203x203x113+</t>
+  </si>
+  <si>
+    <t>203x203x100+</t>
+  </si>
+  <si>
+    <t>152x152x51+</t>
+  </si>
+  <si>
+    <t>152x152x44+</t>
   </si>
 </sst>
 </file>
@@ -231,7 +249,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -242,6 +281,1763 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Structural Steel Section Proper"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Designation</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Mass (kg/m)</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>h (mm)</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>b (mm)</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>tw​ (mm)</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>tf​ (mm)</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>r (mm)</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>d (mm)</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>c/tf​</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>cw​/tw​</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>C (mm)</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>N (mm)</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>n (mm)</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>Area/m (m2)</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>Area/T (m2)</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>152x152x23</v>
+          </cell>
+          <cell r="B2">
+            <v>23</v>
+          </cell>
+          <cell r="C2">
+            <v>152.4</v>
+          </cell>
+          <cell r="D2">
+            <v>152.19999999999999</v>
+          </cell>
+          <cell r="E2">
+            <v>5.8</v>
+          </cell>
+          <cell r="F2">
+            <v>6.8</v>
+          </cell>
+          <cell r="G2">
+            <v>7.6</v>
+          </cell>
+          <cell r="H2">
+            <v>123.6</v>
+          </cell>
+          <cell r="I2">
+            <v>9.65</v>
+          </cell>
+          <cell r="J2">
+            <v>21.3</v>
+          </cell>
+          <cell r="K2">
+            <v>5</v>
+          </cell>
+          <cell r="L2">
+            <v>84</v>
+          </cell>
+          <cell r="M2">
+            <v>16</v>
+          </cell>
+          <cell r="N2">
+            <v>0.88900000000000001</v>
+          </cell>
+          <cell r="O2">
+            <v>38.700000000000003</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>152x152x30</v>
+          </cell>
+          <cell r="B3">
+            <v>30</v>
+          </cell>
+          <cell r="C3">
+            <v>157.6</v>
+          </cell>
+          <cell r="D3">
+            <v>152.9</v>
+          </cell>
+          <cell r="E3">
+            <v>6.5</v>
+          </cell>
+          <cell r="F3">
+            <v>9.4</v>
+          </cell>
+          <cell r="G3">
+            <v>7.6</v>
+          </cell>
+          <cell r="H3">
+            <v>123.6</v>
+          </cell>
+          <cell r="I3">
+            <v>6.98</v>
+          </cell>
+          <cell r="J3">
+            <v>19</v>
+          </cell>
+          <cell r="K3">
+            <v>5</v>
+          </cell>
+          <cell r="L3">
+            <v>84</v>
+          </cell>
+          <cell r="M3">
+            <v>18</v>
+          </cell>
+          <cell r="N3">
+            <v>0.90100000000000002</v>
+          </cell>
+          <cell r="O3">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>152x152x37</v>
+          </cell>
+          <cell r="B4">
+            <v>37</v>
+          </cell>
+          <cell r="C4">
+            <v>161.80000000000001</v>
+          </cell>
+          <cell r="D4">
+            <v>154.4</v>
+          </cell>
+          <cell r="E4">
+            <v>8</v>
+          </cell>
+          <cell r="F4">
+            <v>11.5</v>
+          </cell>
+          <cell r="G4">
+            <v>7.6</v>
+          </cell>
+          <cell r="H4">
+            <v>123.6</v>
+          </cell>
+          <cell r="I4">
+            <v>5.7</v>
+          </cell>
+          <cell r="J4">
+            <v>15.5</v>
+          </cell>
+          <cell r="K4">
+            <v>6</v>
+          </cell>
+          <cell r="L4">
+            <v>84</v>
+          </cell>
+          <cell r="M4">
+            <v>20</v>
+          </cell>
+          <cell r="N4">
+            <v>0.91200000000000003</v>
+          </cell>
+          <cell r="O4">
+            <v>24.7</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>152x152x44+</v>
+          </cell>
+          <cell r="B5">
+            <v>44</v>
+          </cell>
+          <cell r="C5">
+            <v>166</v>
+          </cell>
+          <cell r="D5">
+            <v>155.9</v>
+          </cell>
+          <cell r="E5">
+            <v>9.5</v>
+          </cell>
+          <cell r="F5">
+            <v>13.6</v>
+          </cell>
+          <cell r="G5">
+            <v>7.6</v>
+          </cell>
+          <cell r="H5">
+            <v>123.6</v>
+          </cell>
+          <cell r="I5">
+            <v>4.82</v>
+          </cell>
+          <cell r="J5">
+            <v>13</v>
+          </cell>
+          <cell r="K5">
+            <v>7</v>
+          </cell>
+          <cell r="L5">
+            <v>84</v>
+          </cell>
+          <cell r="M5">
+            <v>22</v>
+          </cell>
+          <cell r="N5">
+            <v>0.92400000000000004</v>
+          </cell>
+          <cell r="O5">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>152x152x51+</v>
+          </cell>
+          <cell r="B6">
+            <v>51.2</v>
+          </cell>
+          <cell r="C6">
+            <v>170.2</v>
+          </cell>
+          <cell r="D6">
+            <v>157.4</v>
+          </cell>
+          <cell r="E6">
+            <v>11</v>
+          </cell>
+          <cell r="F6">
+            <v>15.7</v>
+          </cell>
+          <cell r="G6">
+            <v>7.6</v>
+          </cell>
+          <cell r="H6">
+            <v>123.6</v>
+          </cell>
+          <cell r="I6">
+            <v>4.18</v>
+          </cell>
+          <cell r="J6">
+            <v>11.2</v>
+          </cell>
+          <cell r="K6">
+            <v>8</v>
+          </cell>
+          <cell r="L6">
+            <v>84</v>
+          </cell>
+          <cell r="M6">
+            <v>24</v>
+          </cell>
+          <cell r="N6">
+            <v>0.93500000000000005</v>
+          </cell>
+          <cell r="O6">
+            <v>18.3</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>203x203x46</v>
+          </cell>
+          <cell r="B7">
+            <v>46.1</v>
+          </cell>
+          <cell r="C7">
+            <v>203.2</v>
+          </cell>
+          <cell r="D7">
+            <v>203.6</v>
+          </cell>
+          <cell r="E7">
+            <v>7.2</v>
+          </cell>
+          <cell r="F7">
+            <v>11</v>
+          </cell>
+          <cell r="G7">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H7">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I7">
+            <v>8</v>
+          </cell>
+          <cell r="J7">
+            <v>22.3</v>
+          </cell>
+          <cell r="K7">
+            <v>6</v>
+          </cell>
+          <cell r="L7">
+            <v>110</v>
+          </cell>
+          <cell r="M7">
+            <v>22</v>
+          </cell>
+          <cell r="N7">
+            <v>1.19</v>
+          </cell>
+          <cell r="O7">
+            <v>25.8</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>203x203x52</v>
+          </cell>
+          <cell r="B8">
+            <v>52</v>
+          </cell>
+          <cell r="C8">
+            <v>206.2</v>
+          </cell>
+          <cell r="D8">
+            <v>204.3</v>
+          </cell>
+          <cell r="E8">
+            <v>7.9</v>
+          </cell>
+          <cell r="F8">
+            <v>12.5</v>
+          </cell>
+          <cell r="G8">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H8">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I8">
+            <v>7.04</v>
+          </cell>
+          <cell r="J8">
+            <v>20.399999999999999</v>
+          </cell>
+          <cell r="K8">
+            <v>6</v>
+          </cell>
+          <cell r="L8">
+            <v>110</v>
+          </cell>
+          <cell r="M8">
+            <v>24</v>
+          </cell>
+          <cell r="N8">
+            <v>1.2</v>
+          </cell>
+          <cell r="O8">
+            <v>23.1</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>203x203x60</v>
+          </cell>
+          <cell r="B9">
+            <v>60</v>
+          </cell>
+          <cell r="C9">
+            <v>209.6</v>
+          </cell>
+          <cell r="D9">
+            <v>205.8</v>
+          </cell>
+          <cell r="E9">
+            <v>9.4</v>
+          </cell>
+          <cell r="F9">
+            <v>14.2</v>
+          </cell>
+          <cell r="G9">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H9">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I9">
+            <v>6.2</v>
+          </cell>
+          <cell r="J9">
+            <v>17.100000000000001</v>
+          </cell>
+          <cell r="K9">
+            <v>7</v>
+          </cell>
+          <cell r="L9">
+            <v>110</v>
+          </cell>
+          <cell r="M9">
+            <v>26</v>
+          </cell>
+          <cell r="N9">
+            <v>1.21</v>
+          </cell>
+          <cell r="O9">
+            <v>20.2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>203x203x71</v>
+          </cell>
+          <cell r="B10">
+            <v>71</v>
+          </cell>
+          <cell r="C10">
+            <v>215.8</v>
+          </cell>
+          <cell r="D10">
+            <v>206.4</v>
+          </cell>
+          <cell r="E10">
+            <v>10</v>
+          </cell>
+          <cell r="F10">
+            <v>17.3</v>
+          </cell>
+          <cell r="G10">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H10">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I10">
+            <v>5.09</v>
+          </cell>
+          <cell r="J10">
+            <v>16.100000000000001</v>
+          </cell>
+          <cell r="K10">
+            <v>7</v>
+          </cell>
+          <cell r="L10">
+            <v>110</v>
+          </cell>
+          <cell r="M10">
+            <v>28</v>
+          </cell>
+          <cell r="N10">
+            <v>1.22</v>
+          </cell>
+          <cell r="O10">
+            <v>17.2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>203x203x86</v>
+          </cell>
+          <cell r="B11">
+            <v>86.1</v>
+          </cell>
+          <cell r="C11">
+            <v>222.2</v>
+          </cell>
+          <cell r="D11">
+            <v>209.1</v>
+          </cell>
+          <cell r="E11">
+            <v>12.7</v>
+          </cell>
+          <cell r="F11">
+            <v>20.5</v>
+          </cell>
+          <cell r="G11">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H11">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I11">
+            <v>4.29</v>
+          </cell>
+          <cell r="J11">
+            <v>12.7</v>
+          </cell>
+          <cell r="K11">
+            <v>8</v>
+          </cell>
+          <cell r="L11">
+            <v>110</v>
+          </cell>
+          <cell r="M11">
+            <v>32</v>
+          </cell>
+          <cell r="N11">
+            <v>1.24</v>
+          </cell>
+          <cell r="O11">
+            <v>14.4</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>203x203x100+</v>
+          </cell>
+          <cell r="B12">
+            <v>99.6</v>
+          </cell>
+          <cell r="C12">
+            <v>228.6</v>
+          </cell>
+          <cell r="D12">
+            <v>210.3</v>
+          </cell>
+          <cell r="E12">
+            <v>14.5</v>
+          </cell>
+          <cell r="F12">
+            <v>23.7</v>
+          </cell>
+          <cell r="G12">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H12">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I12">
+            <v>3.7</v>
+          </cell>
+          <cell r="J12">
+            <v>11.1</v>
+          </cell>
+          <cell r="K12">
+            <v>9</v>
+          </cell>
+          <cell r="L12">
+            <v>108</v>
+          </cell>
+          <cell r="M12">
+            <v>34</v>
+          </cell>
+          <cell r="N12">
+            <v>1.25</v>
+          </cell>
+          <cell r="O12">
+            <v>12.6</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>203x203x113+</v>
+          </cell>
+          <cell r="B13">
+            <v>113.5</v>
+          </cell>
+          <cell r="C13">
+            <v>235</v>
+          </cell>
+          <cell r="D13">
+            <v>212.1</v>
+          </cell>
+          <cell r="E13">
+            <v>16.3</v>
+          </cell>
+          <cell r="F13">
+            <v>26.9</v>
+          </cell>
+          <cell r="G13">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H13">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I13">
+            <v>3.26</v>
+          </cell>
+          <cell r="J13">
+            <v>9.8699999999999992</v>
+          </cell>
+          <cell r="K13">
+            <v>10</v>
+          </cell>
+          <cell r="L13">
+            <v>108</v>
+          </cell>
+          <cell r="M13">
+            <v>38</v>
+          </cell>
+          <cell r="N13">
+            <v>1.27</v>
+          </cell>
+          <cell r="O13">
+            <v>11.2</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>203x203x127+</v>
+          </cell>
+          <cell r="B14">
+            <v>127.5</v>
+          </cell>
+          <cell r="C14">
+            <v>241.4</v>
+          </cell>
+          <cell r="D14">
+            <v>213.9</v>
+          </cell>
+          <cell r="E14">
+            <v>18.100000000000001</v>
+          </cell>
+          <cell r="F14">
+            <v>30.1</v>
+          </cell>
+          <cell r="G14">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="H14">
+            <v>160.80000000000001</v>
+          </cell>
+          <cell r="I14">
+            <v>2.91</v>
+          </cell>
+          <cell r="J14">
+            <v>8.8800000000000008</v>
+          </cell>
+          <cell r="K14">
+            <v>11</v>
+          </cell>
+          <cell r="L14">
+            <v>108</v>
+          </cell>
+          <cell r="M14">
+            <v>42</v>
+          </cell>
+          <cell r="N14">
+            <v>1.28</v>
+          </cell>
+          <cell r="O14">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>254x254x73</v>
+          </cell>
+          <cell r="B15">
+            <v>73.099999999999994</v>
+          </cell>
+          <cell r="C15">
+            <v>254.1</v>
+          </cell>
+          <cell r="D15">
+            <v>254.6</v>
+          </cell>
+          <cell r="E15">
+            <v>8.6</v>
+          </cell>
+          <cell r="F15">
+            <v>14.2</v>
+          </cell>
+          <cell r="G15">
+            <v>12.7</v>
+          </cell>
+          <cell r="H15">
+            <v>200.3</v>
+          </cell>
+          <cell r="I15">
+            <v>7.77</v>
+          </cell>
+          <cell r="J15">
+            <v>23.3</v>
+          </cell>
+          <cell r="K15">
+            <v>6</v>
+          </cell>
+          <cell r="L15">
+            <v>134</v>
+          </cell>
+          <cell r="M15">
+            <v>28</v>
+          </cell>
+          <cell r="N15">
+            <v>1.49</v>
+          </cell>
+          <cell r="O15">
+            <v>20.399999999999999</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>254x254x89</v>
+          </cell>
+          <cell r="B16">
+            <v>88.9</v>
+          </cell>
+          <cell r="C16">
+            <v>260.3</v>
+          </cell>
+          <cell r="D16">
+            <v>256.3</v>
+          </cell>
+          <cell r="E16">
+            <v>10.3</v>
+          </cell>
+          <cell r="F16">
+            <v>17.3</v>
+          </cell>
+          <cell r="G16">
+            <v>12.7</v>
+          </cell>
+          <cell r="H16">
+            <v>200.3</v>
+          </cell>
+          <cell r="I16">
+            <v>6.38</v>
+          </cell>
+          <cell r="J16">
+            <v>19.399999999999999</v>
+          </cell>
+          <cell r="K16">
+            <v>7</v>
+          </cell>
+          <cell r="L16">
+            <v>134</v>
+          </cell>
+          <cell r="M16">
+            <v>30</v>
+          </cell>
+          <cell r="N16">
+            <v>1.5</v>
+          </cell>
+          <cell r="O16">
+            <v>16.899999999999999</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>254x254x107</v>
+          </cell>
+          <cell r="B17">
+            <v>107.1</v>
+          </cell>
+          <cell r="C17">
+            <v>266.7</v>
+          </cell>
+          <cell r="D17">
+            <v>258.8</v>
+          </cell>
+          <cell r="E17">
+            <v>12.8</v>
+          </cell>
+          <cell r="F17">
+            <v>20.5</v>
+          </cell>
+          <cell r="G17">
+            <v>12.7</v>
+          </cell>
+          <cell r="H17">
+            <v>200.3</v>
+          </cell>
+          <cell r="I17">
+            <v>5.38</v>
+          </cell>
+          <cell r="J17">
+            <v>15.6</v>
+          </cell>
+          <cell r="K17">
+            <v>8</v>
+          </cell>
+          <cell r="L17">
+            <v>134</v>
+          </cell>
+          <cell r="M17">
+            <v>34</v>
+          </cell>
+          <cell r="N17">
+            <v>1.52</v>
+          </cell>
+          <cell r="O17">
+            <v>14.2</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>254x254x132</v>
+          </cell>
+          <cell r="B18">
+            <v>132</v>
+          </cell>
+          <cell r="C18">
+            <v>276.3</v>
+          </cell>
+          <cell r="D18">
+            <v>261.3</v>
+          </cell>
+          <cell r="E18">
+            <v>15.3</v>
+          </cell>
+          <cell r="F18">
+            <v>25.3</v>
+          </cell>
+          <cell r="G18">
+            <v>12.7</v>
+          </cell>
+          <cell r="H18">
+            <v>200.3</v>
+          </cell>
+          <cell r="I18">
+            <v>4.3600000000000003</v>
+          </cell>
+          <cell r="J18">
+            <v>13.1</v>
+          </cell>
+          <cell r="K18">
+            <v>10</v>
+          </cell>
+          <cell r="L18">
+            <v>134</v>
+          </cell>
+          <cell r="M18">
+            <v>38</v>
+          </cell>
+          <cell r="N18">
+            <v>1.55</v>
+          </cell>
+          <cell r="O18">
+            <v>11.7</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>254x254x167</v>
+          </cell>
+          <cell r="B19">
+            <v>167.1</v>
+          </cell>
+          <cell r="C19">
+            <v>289.10000000000002</v>
+          </cell>
+          <cell r="D19">
+            <v>265.2</v>
+          </cell>
+          <cell r="E19">
+            <v>19.2</v>
+          </cell>
+          <cell r="F19">
+            <v>31.7</v>
+          </cell>
+          <cell r="G19">
+            <v>12.7</v>
+          </cell>
+          <cell r="H19">
+            <v>200.3</v>
+          </cell>
+          <cell r="I19">
+            <v>3.48</v>
+          </cell>
+          <cell r="J19">
+            <v>10.4</v>
+          </cell>
+          <cell r="K19">
+            <v>12</v>
+          </cell>
+          <cell r="L19">
+            <v>134</v>
+          </cell>
+          <cell r="M19">
+            <v>46</v>
+          </cell>
+          <cell r="N19">
+            <v>1.58</v>
+          </cell>
+          <cell r="O19">
+            <v>9.4600000000000009</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>305x305x97</v>
+          </cell>
+          <cell r="B20">
+            <v>96.9</v>
+          </cell>
+          <cell r="C20">
+            <v>307.89999999999998</v>
+          </cell>
+          <cell r="D20">
+            <v>305.3</v>
+          </cell>
+          <cell r="E20">
+            <v>9.9</v>
+          </cell>
+          <cell r="F20">
+            <v>15.4</v>
+          </cell>
+          <cell r="G20">
+            <v>15.2</v>
+          </cell>
+          <cell r="H20">
+            <v>246.7</v>
+          </cell>
+          <cell r="I20">
+            <v>8.6</v>
+          </cell>
+          <cell r="J20">
+            <v>24.9</v>
+          </cell>
+          <cell r="K20">
+            <v>7</v>
+          </cell>
+          <cell r="L20">
+            <v>158</v>
+          </cell>
+          <cell r="M20">
+            <v>32</v>
+          </cell>
+          <cell r="N20">
+            <v>1.79</v>
+          </cell>
+          <cell r="O20">
+            <v>18.5</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>305x305x118</v>
+          </cell>
+          <cell r="B21">
+            <v>117.9</v>
+          </cell>
+          <cell r="C21">
+            <v>314.5</v>
+          </cell>
+          <cell r="D21">
+            <v>307.39999999999998</v>
+          </cell>
+          <cell r="E21">
+            <v>12</v>
+          </cell>
+          <cell r="F21">
+            <v>18.7</v>
+          </cell>
+          <cell r="G21">
+            <v>15.2</v>
+          </cell>
+          <cell r="H21">
+            <v>246.7</v>
+          </cell>
+          <cell r="I21">
+            <v>7.09</v>
+          </cell>
+          <cell r="J21">
+            <v>20.6</v>
+          </cell>
+          <cell r="K21">
+            <v>8</v>
+          </cell>
+          <cell r="L21">
+            <v>158</v>
+          </cell>
+          <cell r="M21">
+            <v>34</v>
+          </cell>
+          <cell r="N21">
+            <v>1.81</v>
+          </cell>
+          <cell r="O21">
+            <v>15.4</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>305x305x137</v>
+          </cell>
+          <cell r="B22">
+            <v>136.9</v>
+          </cell>
+          <cell r="C22">
+            <v>320.5</v>
+          </cell>
+          <cell r="D22">
+            <v>309.2</v>
+          </cell>
+          <cell r="E22">
+            <v>13.8</v>
+          </cell>
+          <cell r="F22">
+            <v>21.7</v>
+          </cell>
+          <cell r="G22">
+            <v>15.2</v>
+          </cell>
+          <cell r="H22">
+            <v>246.7</v>
+          </cell>
+          <cell r="I22">
+            <v>6.11</v>
+          </cell>
+          <cell r="J22">
+            <v>17.899999999999999</v>
+          </cell>
+          <cell r="K22">
+            <v>9</v>
+          </cell>
+          <cell r="L22">
+            <v>158</v>
+          </cell>
+          <cell r="M22">
+            <v>38</v>
+          </cell>
+          <cell r="N22">
+            <v>1.82</v>
+          </cell>
+          <cell r="O22">
+            <v>13.3</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>305x305x158</v>
+          </cell>
+          <cell r="B23">
+            <v>158.1</v>
+          </cell>
+          <cell r="C23">
+            <v>327.10000000000002</v>
+          </cell>
+          <cell r="D23">
+            <v>311.2</v>
+          </cell>
+          <cell r="E23">
+            <v>15.8</v>
+          </cell>
+          <cell r="F23">
+            <v>25</v>
+          </cell>
+          <cell r="G23">
+            <v>15.2</v>
+          </cell>
+          <cell r="H23">
+            <v>246.7</v>
+          </cell>
+          <cell r="I23">
+            <v>5.3</v>
+          </cell>
+          <cell r="J23">
+            <v>15.6</v>
+          </cell>
+          <cell r="K23">
+            <v>10</v>
+          </cell>
+          <cell r="L23">
+            <v>158</v>
+          </cell>
+          <cell r="M23">
+            <v>42</v>
+          </cell>
+          <cell r="N23">
+            <v>1.84</v>
+          </cell>
+          <cell r="O23">
+            <v>11.6</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>305x305x198</v>
+          </cell>
+          <cell r="B24">
+            <v>198.1</v>
+          </cell>
+          <cell r="C24">
+            <v>339.9</v>
+          </cell>
+          <cell r="D24">
+            <v>314.5</v>
+          </cell>
+          <cell r="E24">
+            <v>19.100000000000001</v>
+          </cell>
+          <cell r="F24">
+            <v>31.4</v>
+          </cell>
+          <cell r="G24">
+            <v>15.2</v>
+          </cell>
+          <cell r="H24">
+            <v>246.7</v>
+          </cell>
+          <cell r="I24">
+            <v>4.22</v>
+          </cell>
+          <cell r="J24">
+            <v>12.9</v>
+          </cell>
+          <cell r="K24">
+            <v>12</v>
+          </cell>
+          <cell r="L24">
+            <v>158</v>
+          </cell>
+          <cell r="M24">
+            <v>48</v>
+          </cell>
+          <cell r="N24">
+            <v>1.87</v>
+          </cell>
+          <cell r="O24">
+            <v>9.44</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>305x305x240</v>
+          </cell>
+          <cell r="B25">
+            <v>240</v>
+          </cell>
+          <cell r="C25">
+            <v>352.5</v>
+          </cell>
+          <cell r="D25">
+            <v>318.39999999999998</v>
+          </cell>
+          <cell r="E25">
+            <v>23</v>
+          </cell>
+          <cell r="F25">
+            <v>37.700000000000003</v>
+          </cell>
+          <cell r="G25">
+            <v>15.2</v>
+          </cell>
+          <cell r="H25">
+            <v>246.7</v>
+          </cell>
+          <cell r="I25">
+            <v>3.51</v>
+          </cell>
+          <cell r="J25">
+            <v>10.7</v>
+          </cell>
+          <cell r="K25">
+            <v>14</v>
+          </cell>
+          <cell r="L25">
+            <v>158</v>
+          </cell>
+          <cell r="M25">
+            <v>54</v>
+          </cell>
+          <cell r="N25">
+            <v>1.91</v>
+          </cell>
+          <cell r="O25">
+            <v>7.96</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>305x305x283</v>
+          </cell>
+          <cell r="B26">
+            <v>282.89999999999998</v>
+          </cell>
+          <cell r="C26">
+            <v>365.3</v>
+          </cell>
+          <cell r="D26">
+            <v>322.2</v>
+          </cell>
+          <cell r="E26">
+            <v>26.8</v>
+          </cell>
+          <cell r="F26">
+            <v>44.1</v>
+          </cell>
+          <cell r="G26">
+            <v>15.2</v>
+          </cell>
+          <cell r="H26">
+            <v>246.7</v>
+          </cell>
+          <cell r="I26">
+            <v>3</v>
+          </cell>
+          <cell r="J26">
+            <v>9.2100000000000009</v>
+          </cell>
+          <cell r="K26">
+            <v>15</v>
+          </cell>
+          <cell r="L26">
+            <v>158</v>
+          </cell>
+          <cell r="M26">
+            <v>60</v>
+          </cell>
+          <cell r="N26">
+            <v>1.94</v>
+          </cell>
+          <cell r="O26">
+            <v>6.86</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>356x368x129</v>
+          </cell>
+          <cell r="B27">
+            <v>129</v>
+          </cell>
+          <cell r="C27">
+            <v>355.6</v>
+          </cell>
+          <cell r="D27">
+            <v>368.6</v>
+          </cell>
+          <cell r="E27">
+            <v>10.4</v>
+          </cell>
+          <cell r="F27">
+            <v>17.5</v>
+          </cell>
+          <cell r="G27">
+            <v>15.2</v>
+          </cell>
+          <cell r="H27">
+            <v>290.2</v>
+          </cell>
+          <cell r="I27">
+            <v>9.4</v>
+          </cell>
+          <cell r="J27">
+            <v>27.9</v>
+          </cell>
+          <cell r="K27">
+            <v>7</v>
+          </cell>
+          <cell r="L27">
+            <v>190</v>
+          </cell>
+          <cell r="M27">
+            <v>34</v>
+          </cell>
+          <cell r="N27">
+            <v>2.14</v>
+          </cell>
+          <cell r="O27">
+            <v>16.600000000000001</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>356x368x153</v>
+          </cell>
+          <cell r="B28">
+            <v>152.9</v>
+          </cell>
+          <cell r="C28">
+            <v>362</v>
+          </cell>
+          <cell r="D28">
+            <v>370.5</v>
+          </cell>
+          <cell r="E28">
+            <v>12.3</v>
+          </cell>
+          <cell r="F28">
+            <v>20.7</v>
+          </cell>
+          <cell r="G28">
+            <v>15.2</v>
+          </cell>
+          <cell r="H28">
+            <v>290.2</v>
+          </cell>
+          <cell r="I28">
+            <v>7.92</v>
+          </cell>
+          <cell r="J28">
+            <v>23.6</v>
+          </cell>
+          <cell r="K28">
+            <v>8</v>
+          </cell>
+          <cell r="L28">
+            <v>190</v>
+          </cell>
+          <cell r="M28">
+            <v>36</v>
+          </cell>
+          <cell r="N28">
+            <v>2.16</v>
+          </cell>
+          <cell r="O28">
+            <v>14.1</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>356x368x177</v>
+          </cell>
+          <cell r="B29">
+            <v>177</v>
+          </cell>
+          <cell r="C29">
+            <v>368.2</v>
+          </cell>
+          <cell r="D29">
+            <v>372.6</v>
+          </cell>
+          <cell r="E29">
+            <v>14.4</v>
+          </cell>
+          <cell r="F29">
+            <v>23.8</v>
+          </cell>
+          <cell r="G29">
+            <v>15.2</v>
+          </cell>
+          <cell r="H29">
+            <v>290.2</v>
+          </cell>
+          <cell r="I29">
+            <v>6.89</v>
+          </cell>
+          <cell r="J29">
+            <v>20.2</v>
+          </cell>
+          <cell r="K29">
+            <v>9</v>
+          </cell>
+          <cell r="L29">
+            <v>190</v>
+          </cell>
+          <cell r="M29">
+            <v>40</v>
+          </cell>
+          <cell r="N29">
+            <v>2.17</v>
+          </cell>
+          <cell r="O29">
+            <v>12.3</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>356x368x202</v>
+          </cell>
+          <cell r="B30">
+            <v>201.9</v>
+          </cell>
+          <cell r="C30">
+            <v>374.6</v>
+          </cell>
+          <cell r="D30">
+            <v>374.7</v>
+          </cell>
+          <cell r="E30">
+            <v>16.5</v>
+          </cell>
+          <cell r="F30">
+            <v>27</v>
+          </cell>
+          <cell r="G30">
+            <v>15.2</v>
+          </cell>
+          <cell r="H30">
+            <v>290.2</v>
+          </cell>
+          <cell r="I30">
+            <v>6.07</v>
+          </cell>
+          <cell r="J30">
+            <v>17.600000000000001</v>
+          </cell>
+          <cell r="K30">
+            <v>10</v>
+          </cell>
+          <cell r="L30">
+            <v>190</v>
+          </cell>
+          <cell r="M30">
+            <v>44</v>
+          </cell>
+          <cell r="N30">
+            <v>2.19</v>
+          </cell>
+          <cell r="O30">
+            <v>10.8</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>356x406x235</v>
+          </cell>
+          <cell r="B31">
+            <v>235.1</v>
+          </cell>
+          <cell r="C31">
+            <v>381</v>
+          </cell>
+          <cell r="D31">
+            <v>394.8</v>
+          </cell>
+          <cell r="E31">
+            <v>18.399999999999999</v>
+          </cell>
+          <cell r="F31">
+            <v>30.2</v>
+          </cell>
+          <cell r="G31">
+            <v>15.2</v>
+          </cell>
+          <cell r="H31">
+            <v>290.2</v>
+          </cell>
+          <cell r="I31">
+            <v>5.73</v>
+          </cell>
+          <cell r="J31">
+            <v>15.8</v>
+          </cell>
+          <cell r="K31">
+            <v>11</v>
+          </cell>
+          <cell r="L31">
+            <v>200</v>
+          </cell>
+          <cell r="M31">
+            <v>46</v>
+          </cell>
+          <cell r="N31">
+            <v>2.2799999999999998</v>
+          </cell>
+          <cell r="O31">
+            <v>9.6999999999999993</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>356x406x287</v>
+          </cell>
+          <cell r="B32">
+            <v>287.10000000000002</v>
+          </cell>
+          <cell r="C32">
+            <v>393.6</v>
+          </cell>
+          <cell r="D32">
+            <v>399</v>
+          </cell>
+          <cell r="E32">
+            <v>22.6</v>
+          </cell>
+          <cell r="F32">
+            <v>36.5</v>
+          </cell>
+          <cell r="G32">
+            <v>15.2</v>
+          </cell>
+          <cell r="H32">
+            <v>290.2</v>
+          </cell>
+          <cell r="I32">
+            <v>4.74</v>
+          </cell>
+          <cell r="J32">
+            <v>12.8</v>
+          </cell>
+          <cell r="K32">
+            <v>13</v>
+          </cell>
+          <cell r="L32">
+            <v>200</v>
+          </cell>
+          <cell r="M32">
+            <v>52</v>
+          </cell>
+          <cell r="N32">
+            <v>2.31</v>
+          </cell>
+          <cell r="O32">
+            <v>8.0500000000000007</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>356x406x340</v>
+          </cell>
+          <cell r="B33">
+            <v>339.9</v>
+          </cell>
+          <cell r="C33">
+            <v>406.4</v>
+          </cell>
+          <cell r="D33">
+            <v>403</v>
+          </cell>
+          <cell r="E33">
+            <v>26.6</v>
+          </cell>
+          <cell r="F33">
+            <v>42.9</v>
+          </cell>
+          <cell r="G33">
+            <v>15.2</v>
+          </cell>
+          <cell r="H33">
+            <v>290.2</v>
+          </cell>
+          <cell r="I33">
+            <v>4.03</v>
+          </cell>
+          <cell r="J33">
+            <v>10.9</v>
+          </cell>
+          <cell r="K33">
+            <v>15</v>
+          </cell>
+          <cell r="L33">
+            <v>200</v>
+          </cell>
+          <cell r="M33">
+            <v>60</v>
+          </cell>
+          <cell r="N33">
+            <v>2.35</v>
+          </cell>
+          <cell r="O33">
+            <v>6.91</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>356x406x393</v>
+          </cell>
+          <cell r="B34">
+            <v>393</v>
+          </cell>
+          <cell r="C34">
+            <v>419</v>
+          </cell>
+          <cell r="D34">
+            <v>407</v>
+          </cell>
+          <cell r="E34">
+            <v>30.6</v>
+          </cell>
+          <cell r="F34">
+            <v>49.2</v>
+          </cell>
+          <cell r="G34">
+            <v>15.2</v>
+          </cell>
+          <cell r="H34">
+            <v>290.2</v>
+          </cell>
+          <cell r="I34">
+            <v>3.52</v>
+          </cell>
+          <cell r="J34">
+            <v>9.48</v>
+          </cell>
+          <cell r="K34">
+            <v>17</v>
+          </cell>
+          <cell r="L34">
+            <v>200</v>
+          </cell>
+          <cell r="M34">
+            <v>66</v>
+          </cell>
+          <cell r="N34">
+            <v>2.38</v>
+          </cell>
+          <cell r="O34">
+            <v>6.06</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>356x406x467</v>
+          </cell>
+          <cell r="B35">
+            <v>467</v>
+          </cell>
+          <cell r="C35">
+            <v>436.6</v>
+          </cell>
+          <cell r="D35">
+            <v>412.2</v>
+          </cell>
+          <cell r="E35">
+            <v>35.799999999999997</v>
+          </cell>
+          <cell r="F35">
+            <v>58</v>
+          </cell>
+          <cell r="G35">
+            <v>15.2</v>
+          </cell>
+          <cell r="H35">
+            <v>290.2</v>
+          </cell>
+          <cell r="I35">
+            <v>2.98</v>
+          </cell>
+          <cell r="J35">
+            <v>8.11</v>
+          </cell>
+          <cell r="K35">
+            <v>20</v>
+          </cell>
+          <cell r="L35">
+            <v>200</v>
+          </cell>
+          <cell r="M35">
+            <v>74</v>
+          </cell>
+          <cell r="N35">
+            <v>2.42</v>
+          </cell>
+          <cell r="O35">
+            <v>5.18</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>356x406x551</v>
+          </cell>
+          <cell r="B36">
+            <v>551</v>
+          </cell>
+          <cell r="C36">
+            <v>455.6</v>
+          </cell>
+          <cell r="D36">
+            <v>418.5</v>
+          </cell>
+          <cell r="E36">
+            <v>42.1</v>
+          </cell>
+          <cell r="F36">
+            <v>67.5</v>
+          </cell>
+          <cell r="G36">
+            <v>15.2</v>
+          </cell>
+          <cell r="H36">
+            <v>290.2</v>
+          </cell>
+          <cell r="I36">
+            <v>2.56</v>
+          </cell>
+          <cell r="J36">
+            <v>6.89</v>
+          </cell>
+          <cell r="K36">
+            <v>23</v>
+          </cell>
+          <cell r="L36">
+            <v>200</v>
+          </cell>
+          <cell r="M36">
+            <v>84</v>
+          </cell>
+          <cell r="N36">
+            <v>2.4700000000000002</v>
+          </cell>
+          <cell r="O36">
+            <v>4.4800000000000004</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>356x406x634</v>
+          </cell>
+          <cell r="B37">
+            <v>633.9</v>
+          </cell>
+          <cell r="C37">
+            <v>474.6</v>
+          </cell>
+          <cell r="D37">
+            <v>424</v>
+          </cell>
+          <cell r="E37">
+            <v>47.6</v>
+          </cell>
+          <cell r="F37">
+            <v>77</v>
+          </cell>
+          <cell r="G37">
+            <v>15.2</v>
+          </cell>
+          <cell r="H37">
+            <v>290.2</v>
+          </cell>
+          <cell r="I37">
+            <v>2.25</v>
+          </cell>
+          <cell r="J37">
+            <v>6.1</v>
+          </cell>
+          <cell r="K37">
+            <v>26</v>
+          </cell>
+          <cell r="L37">
+            <v>200</v>
+          </cell>
+          <cell r="M37">
+            <v>94</v>
+          </cell>
+          <cell r="N37">
+            <v>2.52</v>
+          </cell>
+          <cell r="O37">
+            <v>3.98</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -445,10 +2241,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,8 +2287,23 @@
       <c r="N1" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
@@ -535,8 +2346,24 @@
       <c r="N2" s="1">
         <v>2920</v>
       </c>
+      <c r="O2">
+        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>5.8</v>
+      </c>
+      <c r="P2">
+        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>152.4</v>
+      </c>
+      <c r="Q2">
+        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>6.8</v>
+      </c>
+      <c r="S2">
+        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>152.19999999999999</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
@@ -579,8 +2406,24 @@
       <c r="N3" s="1">
         <v>3829.9999999999995</v>
       </c>
+      <c r="O3">
+        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>6.5</v>
+      </c>
+      <c r="P3">
+        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>157.6</v>
+      </c>
+      <c r="Q3">
+        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>9.4</v>
+      </c>
+      <c r="S3">
+        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>152.9</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -623,10 +2466,26 @@
       <c r="N4" s="1">
         <v>4710</v>
       </c>
+      <c r="O4">
+        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="P4">
+        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>161.80000000000001</v>
+      </c>
+      <c r="Q4">
+        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>11.5</v>
+      </c>
+      <c r="S4">
+        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>154.4</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B5" s="1">
         <v>2700</v>
@@ -667,8 +2526,24 @@
       <c r="N5" s="1">
         <v>5610</v>
       </c>
+      <c r="O5">
+        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>9.5</v>
+      </c>
+      <c r="P5">
+        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>166</v>
+      </c>
+      <c r="Q5">
+        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>13.6</v>
+      </c>
+      <c r="S5">
+        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>155.9</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -711,10 +2586,26 @@
       <c r="N6" s="1">
         <v>5870</v>
       </c>
+      <c r="O6">
+        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>7.2</v>
+      </c>
+      <c r="P6">
+        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>203.2</v>
+      </c>
+      <c r="Q6">
+        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="S6">
+        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>203.6</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1">
         <v>3230</v>
@@ -755,8 +2646,24 @@
       <c r="N7" s="1">
         <v>6520</v>
       </c>
+      <c r="O7">
+        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="P7">
+        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>170.2</v>
+      </c>
+      <c r="Q7">
+        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>15.7</v>
+      </c>
+      <c r="S7">
+        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>157.4</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -799,8 +2706,24 @@
       <c r="N8" s="1">
         <v>6630</v>
       </c>
+      <c r="O8">
+        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>7.9</v>
+      </c>
+      <c r="P8">
+        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>206.2</v>
+      </c>
+      <c r="Q8">
+        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S8">
+        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>204.3</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -843,8 +2766,24 @@
       <c r="N9" s="1">
         <v>7640.0000000000009</v>
       </c>
+      <c r="O9">
+        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>9.4</v>
+      </c>
+      <c r="P9">
+        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>209.6</v>
+      </c>
+      <c r="Q9">
+        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>14.2</v>
+      </c>
+      <c r="S9">
+        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>205.8</v>
+      </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -887,8 +2826,24 @@
       <c r="N10" s="1">
         <v>9040</v>
       </c>
+      <c r="O10">
+        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="P10">
+        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>215.8</v>
+      </c>
+      <c r="Q10">
+        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>17.3</v>
+      </c>
+      <c r="S10">
+        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>206.4</v>
+      </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -931,8 +2886,24 @@
       <c r="N11" s="1">
         <v>9310</v>
       </c>
+      <c r="O11">
+        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>8.6</v>
+      </c>
+      <c r="P11">
+        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>254.1</v>
+      </c>
+      <c r="Q11">
+        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>14.2</v>
+      </c>
+      <c r="S11">
+        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>254.6</v>
+      </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -975,8 +2946,24 @@
       <c r="N12" s="1">
         <v>11000</v>
       </c>
+      <c r="O12">
+        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>12.7</v>
+      </c>
+      <c r="P12">
+        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>222.2</v>
+      </c>
+      <c r="Q12">
+        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>20.5</v>
+      </c>
+      <c r="S12">
+        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>209.1</v>
+      </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1019,8 +3006,24 @@
       <c r="N13" s="1">
         <v>11300</v>
       </c>
+      <c r="O13">
+        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>10.3</v>
+      </c>
+      <c r="P13">
+        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>260.3</v>
+      </c>
+      <c r="Q13">
+        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>17.3</v>
+      </c>
+      <c r="S13">
+        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>256.3</v>
+      </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -1063,10 +3066,26 @@
       <c r="N14" s="1">
         <v>12300</v>
       </c>
+      <c r="O14">
+        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>9.9</v>
+      </c>
+      <c r="P14">
+        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>307.89999999999998</v>
+      </c>
+      <c r="Q14">
+        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>15.4</v>
+      </c>
+      <c r="S14">
+        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>305.3</v>
+      </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B15" s="1">
         <v>11300</v>
@@ -1107,8 +3126,24 @@
       <c r="N15" s="1">
         <v>12700</v>
       </c>
+      <c r="O15">
+        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>14.5</v>
+      </c>
+      <c r="P15">
+        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>228.6</v>
+      </c>
+      <c r="Q15">
+        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>23.7</v>
+      </c>
+      <c r="S15">
+        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>210.3</v>
+      </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -1151,10 +3186,26 @@
       <c r="N16" s="1">
         <v>13600</v>
       </c>
+      <c r="O16">
+        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>12.8</v>
+      </c>
+      <c r="P16">
+        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>266.7</v>
+      </c>
+      <c r="Q16">
+        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>20.5</v>
+      </c>
+      <c r="S16">
+        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>258.8</v>
+      </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1">
         <v>13300</v>
@@ -1195,8 +3246,24 @@
       <c r="N17" s="1">
         <v>14500</v>
       </c>
+      <c r="O17">
+        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>16.3</v>
+      </c>
+      <c r="P17">
+        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>235</v>
+      </c>
+      <c r="Q17">
+        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>26.9</v>
+      </c>
+      <c r="S17">
+        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>212.1</v>
+      </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
@@ -1239,10 +3306,26 @@
       <c r="N18" s="1">
         <v>15000</v>
       </c>
+      <c r="O18">
+        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="P18">
+        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>314.5</v>
+      </c>
+      <c r="Q18">
+        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>18.7</v>
+      </c>
+      <c r="S18">
+        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>307.39999999999998</v>
+      </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1">
         <v>15400</v>
@@ -1283,8 +3366,24 @@
       <c r="N19" s="1">
         <v>16200</v>
       </c>
+      <c r="O19">
+        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="P19">
+        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>241.4</v>
+      </c>
+      <c r="Q19">
+        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>30.1</v>
+      </c>
+      <c r="S19">
+        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>213.9</v>
+      </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1327,8 +3426,24 @@
       <c r="N20" s="1">
         <v>16400</v>
       </c>
+      <c r="O20">
+        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>10.4</v>
+      </c>
+      <c r="P20">
+        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>355.6</v>
+      </c>
+      <c r="Q20">
+        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>17.5</v>
+      </c>
+      <c r="S20">
+        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>368.6</v>
+      </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
@@ -1371,8 +3486,24 @@
       <c r="N21" s="1">
         <v>16800</v>
       </c>
+      <c r="O21">
+        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>15.3</v>
+      </c>
+      <c r="P21">
+        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>276.3</v>
+      </c>
+      <c r="Q21">
+        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>25.3</v>
+      </c>
+      <c r="S21">
+        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>261.3</v>
+      </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1415,8 +3546,24 @@
       <c r="N22" s="1">
         <v>17400</v>
       </c>
+      <c r="O22">
+        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>13.8</v>
+      </c>
+      <c r="P22">
+        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>320.5</v>
+      </c>
+      <c r="Q22">
+        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>21.7</v>
+      </c>
+      <c r="S22">
+        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>309.2</v>
+      </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1459,8 +3606,24 @@
       <c r="N23" s="1">
         <v>19500</v>
       </c>
+      <c r="O23">
+        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>12.3</v>
+      </c>
+      <c r="P23">
+        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>362</v>
+      </c>
+      <c r="Q23">
+        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>20.7</v>
+      </c>
+      <c r="S23">
+        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>370.5</v>
+      </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1503,8 +3666,24 @@
       <c r="N24" s="1">
         <v>20100</v>
       </c>
+      <c r="O24">
+        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>15.8</v>
+      </c>
+      <c r="P24">
+        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>327.10000000000002</v>
+      </c>
+      <c r="Q24">
+        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>25</v>
+      </c>
+      <c r="S24">
+        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>311.2</v>
+      </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1547,8 +3726,24 @@
       <c r="N25" s="1">
         <v>21300</v>
       </c>
+      <c r="O25">
+        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>19.2</v>
+      </c>
+      <c r="P25">
+        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>289.10000000000002</v>
+      </c>
+      <c r="Q25">
+        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>31.7</v>
+      </c>
+      <c r="S25">
+        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>265.2</v>
+      </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1591,8 +3786,24 @@
       <c r="N26" s="1">
         <v>22600</v>
       </c>
+      <c r="O26">
+        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>14.4</v>
+      </c>
+      <c r="P26">
+        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>368.2</v>
+      </c>
+      <c r="Q26">
+        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>23.8</v>
+      </c>
+      <c r="S26">
+        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>372.6</v>
+      </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,8 +3846,24 @@
       <c r="N27" s="1">
         <v>25200</v>
       </c>
+      <c r="O27">
+        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="P27">
+        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>339.9</v>
+      </c>
+      <c r="Q27">
+        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>31.4</v>
+      </c>
+      <c r="S27">
+        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>314.5</v>
+      </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
@@ -1679,8 +3906,24 @@
       <c r="N28" s="1">
         <v>25700</v>
       </c>
+      <c r="O28">
+        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>16.5</v>
+      </c>
+      <c r="P28">
+        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>374.6</v>
+      </c>
+      <c r="Q28">
+        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>27</v>
+      </c>
+      <c r="S28">
+        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>374.7</v>
+      </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -1723,8 +3966,24 @@
       <c r="N29" s="1">
         <v>29900</v>
       </c>
+      <c r="O29">
+        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="P29">
+        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>381</v>
+      </c>
+      <c r="Q29">
+        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>30.2</v>
+      </c>
+      <c r="S29">
+        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>394.8</v>
+      </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1767,8 +4026,24 @@
       <c r="N30" s="1">
         <v>30600</v>
       </c>
+      <c r="O30">
+        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>23</v>
+      </c>
+      <c r="P30">
+        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>352.5</v>
+      </c>
+      <c r="Q30">
+        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>37.700000000000003</v>
+      </c>
+      <c r="S30">
+        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>318.39999999999998</v>
+      </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>24</v>
       </c>
@@ -1811,8 +4086,24 @@
       <c r="N31" s="1">
         <v>36000</v>
       </c>
+      <c r="O31">
+        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>26.8</v>
+      </c>
+      <c r="P31">
+        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>365.3</v>
+      </c>
+      <c r="Q31">
+        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>44.1</v>
+      </c>
+      <c r="S31">
+        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>322.2</v>
+      </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -1855,8 +4146,24 @@
       <c r="N32" s="1">
         <v>36600</v>
       </c>
+      <c r="O32">
+        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>22.6</v>
+      </c>
+      <c r="P32">
+        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>393.6</v>
+      </c>
+      <c r="Q32">
+        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>36.5</v>
+      </c>
+      <c r="S32">
+        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>399</v>
+      </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
@@ -1899,8 +4206,24 @@
       <c r="N33" s="1">
         <v>43300</v>
       </c>
+      <c r="O33">
+        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>26.6</v>
+      </c>
+      <c r="P33">
+        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>406.4</v>
+      </c>
+      <c r="Q33">
+        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>42.9</v>
+      </c>
+      <c r="S33">
+        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>403</v>
+      </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>16</v>
       </c>
@@ -1943,8 +4266,24 @@
       <c r="N34" s="1">
         <v>50100</v>
       </c>
+      <c r="O34">
+        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>30.6</v>
+      </c>
+      <c r="P34">
+        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>419</v>
+      </c>
+      <c r="Q34">
+        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>49.2</v>
+      </c>
+      <c r="S34">
+        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>407</v>
+      </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>15</v>
       </c>
@@ -1987,8 +4326,24 @@
       <c r="N35" s="1">
         <v>59500</v>
       </c>
+      <c r="O35">
+        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>35.799999999999997</v>
+      </c>
+      <c r="P35">
+        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>436.6</v>
+      </c>
+      <c r="Q35">
+        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>58</v>
+      </c>
+      <c r="S35">
+        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>412.2</v>
+      </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>14</v>
       </c>
@@ -2031,8 +4386,24 @@
       <c r="N36" s="1">
         <v>70200</v>
       </c>
+      <c r="O36">
+        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>42.1</v>
+      </c>
+      <c r="P36">
+        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>455.6</v>
+      </c>
+      <c r="Q36">
+        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>67.5</v>
+      </c>
+      <c r="S36">
+        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>418.5</v>
+      </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -2074,6 +4445,22 @@
       </c>
       <c r="N37" s="1">
         <v>80800</v>
+      </c>
+      <c r="O37">
+        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
+        <v>47.6</v>
+      </c>
+      <c r="P37">
+        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
+        <v>474.6</v>
+      </c>
+      <c r="Q37">
+        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
+        <v>77</v>
+      </c>
+      <c r="S37">
+        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/UC-2.xlsx
+++ b/UC-2.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Documents/GitHub/g6-analysis-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC9A519-2414-9641-BEFF-8533E2FAB906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C010B2C2-30E0-C245-A7D8-E0DED081FC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Structural Steel Section Proper" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -249,28 +246,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -281,1763 +257,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Structural Steel Section Proper"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Designation</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>Mass (kg/m)</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>h (mm)</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>b (mm)</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>tw​ (mm)</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>tf​ (mm)</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>r (mm)</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>d (mm)</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>c/tf​</v>
-          </cell>
-          <cell r="J1" t="str">
-            <v>cw​/tw​</v>
-          </cell>
-          <cell r="K1" t="str">
-            <v>C (mm)</v>
-          </cell>
-          <cell r="L1" t="str">
-            <v>N (mm)</v>
-          </cell>
-          <cell r="M1" t="str">
-            <v>n (mm)</v>
-          </cell>
-          <cell r="N1" t="str">
-            <v>Area/m (m2)</v>
-          </cell>
-          <cell r="O1" t="str">
-            <v>Area/T (m2)</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>152x152x23</v>
-          </cell>
-          <cell r="B2">
-            <v>23</v>
-          </cell>
-          <cell r="C2">
-            <v>152.4</v>
-          </cell>
-          <cell r="D2">
-            <v>152.19999999999999</v>
-          </cell>
-          <cell r="E2">
-            <v>5.8</v>
-          </cell>
-          <cell r="F2">
-            <v>6.8</v>
-          </cell>
-          <cell r="G2">
-            <v>7.6</v>
-          </cell>
-          <cell r="H2">
-            <v>123.6</v>
-          </cell>
-          <cell r="I2">
-            <v>9.65</v>
-          </cell>
-          <cell r="J2">
-            <v>21.3</v>
-          </cell>
-          <cell r="K2">
-            <v>5</v>
-          </cell>
-          <cell r="L2">
-            <v>84</v>
-          </cell>
-          <cell r="M2">
-            <v>16</v>
-          </cell>
-          <cell r="N2">
-            <v>0.88900000000000001</v>
-          </cell>
-          <cell r="O2">
-            <v>38.700000000000003</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>152x152x30</v>
-          </cell>
-          <cell r="B3">
-            <v>30</v>
-          </cell>
-          <cell r="C3">
-            <v>157.6</v>
-          </cell>
-          <cell r="D3">
-            <v>152.9</v>
-          </cell>
-          <cell r="E3">
-            <v>6.5</v>
-          </cell>
-          <cell r="F3">
-            <v>9.4</v>
-          </cell>
-          <cell r="G3">
-            <v>7.6</v>
-          </cell>
-          <cell r="H3">
-            <v>123.6</v>
-          </cell>
-          <cell r="I3">
-            <v>6.98</v>
-          </cell>
-          <cell r="J3">
-            <v>19</v>
-          </cell>
-          <cell r="K3">
-            <v>5</v>
-          </cell>
-          <cell r="L3">
-            <v>84</v>
-          </cell>
-          <cell r="M3">
-            <v>18</v>
-          </cell>
-          <cell r="N3">
-            <v>0.90100000000000002</v>
-          </cell>
-          <cell r="O3">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>152x152x37</v>
-          </cell>
-          <cell r="B4">
-            <v>37</v>
-          </cell>
-          <cell r="C4">
-            <v>161.80000000000001</v>
-          </cell>
-          <cell r="D4">
-            <v>154.4</v>
-          </cell>
-          <cell r="E4">
-            <v>8</v>
-          </cell>
-          <cell r="F4">
-            <v>11.5</v>
-          </cell>
-          <cell r="G4">
-            <v>7.6</v>
-          </cell>
-          <cell r="H4">
-            <v>123.6</v>
-          </cell>
-          <cell r="I4">
-            <v>5.7</v>
-          </cell>
-          <cell r="J4">
-            <v>15.5</v>
-          </cell>
-          <cell r="K4">
-            <v>6</v>
-          </cell>
-          <cell r="L4">
-            <v>84</v>
-          </cell>
-          <cell r="M4">
-            <v>20</v>
-          </cell>
-          <cell r="N4">
-            <v>0.91200000000000003</v>
-          </cell>
-          <cell r="O4">
-            <v>24.7</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>152x152x44+</v>
-          </cell>
-          <cell r="B5">
-            <v>44</v>
-          </cell>
-          <cell r="C5">
-            <v>166</v>
-          </cell>
-          <cell r="D5">
-            <v>155.9</v>
-          </cell>
-          <cell r="E5">
-            <v>9.5</v>
-          </cell>
-          <cell r="F5">
-            <v>13.6</v>
-          </cell>
-          <cell r="G5">
-            <v>7.6</v>
-          </cell>
-          <cell r="H5">
-            <v>123.6</v>
-          </cell>
-          <cell r="I5">
-            <v>4.82</v>
-          </cell>
-          <cell r="J5">
-            <v>13</v>
-          </cell>
-          <cell r="K5">
-            <v>7</v>
-          </cell>
-          <cell r="L5">
-            <v>84</v>
-          </cell>
-          <cell r="M5">
-            <v>22</v>
-          </cell>
-          <cell r="N5">
-            <v>0.92400000000000004</v>
-          </cell>
-          <cell r="O5">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>152x152x51+</v>
-          </cell>
-          <cell r="B6">
-            <v>51.2</v>
-          </cell>
-          <cell r="C6">
-            <v>170.2</v>
-          </cell>
-          <cell r="D6">
-            <v>157.4</v>
-          </cell>
-          <cell r="E6">
-            <v>11</v>
-          </cell>
-          <cell r="F6">
-            <v>15.7</v>
-          </cell>
-          <cell r="G6">
-            <v>7.6</v>
-          </cell>
-          <cell r="H6">
-            <v>123.6</v>
-          </cell>
-          <cell r="I6">
-            <v>4.18</v>
-          </cell>
-          <cell r="J6">
-            <v>11.2</v>
-          </cell>
-          <cell r="K6">
-            <v>8</v>
-          </cell>
-          <cell r="L6">
-            <v>84</v>
-          </cell>
-          <cell r="M6">
-            <v>24</v>
-          </cell>
-          <cell r="N6">
-            <v>0.93500000000000005</v>
-          </cell>
-          <cell r="O6">
-            <v>18.3</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>203x203x46</v>
-          </cell>
-          <cell r="B7">
-            <v>46.1</v>
-          </cell>
-          <cell r="C7">
-            <v>203.2</v>
-          </cell>
-          <cell r="D7">
-            <v>203.6</v>
-          </cell>
-          <cell r="E7">
-            <v>7.2</v>
-          </cell>
-          <cell r="F7">
-            <v>11</v>
-          </cell>
-          <cell r="G7">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H7">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I7">
-            <v>8</v>
-          </cell>
-          <cell r="J7">
-            <v>22.3</v>
-          </cell>
-          <cell r="K7">
-            <v>6</v>
-          </cell>
-          <cell r="L7">
-            <v>110</v>
-          </cell>
-          <cell r="M7">
-            <v>22</v>
-          </cell>
-          <cell r="N7">
-            <v>1.19</v>
-          </cell>
-          <cell r="O7">
-            <v>25.8</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>203x203x52</v>
-          </cell>
-          <cell r="B8">
-            <v>52</v>
-          </cell>
-          <cell r="C8">
-            <v>206.2</v>
-          </cell>
-          <cell r="D8">
-            <v>204.3</v>
-          </cell>
-          <cell r="E8">
-            <v>7.9</v>
-          </cell>
-          <cell r="F8">
-            <v>12.5</v>
-          </cell>
-          <cell r="G8">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H8">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I8">
-            <v>7.04</v>
-          </cell>
-          <cell r="J8">
-            <v>20.399999999999999</v>
-          </cell>
-          <cell r="K8">
-            <v>6</v>
-          </cell>
-          <cell r="L8">
-            <v>110</v>
-          </cell>
-          <cell r="M8">
-            <v>24</v>
-          </cell>
-          <cell r="N8">
-            <v>1.2</v>
-          </cell>
-          <cell r="O8">
-            <v>23.1</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>203x203x60</v>
-          </cell>
-          <cell r="B9">
-            <v>60</v>
-          </cell>
-          <cell r="C9">
-            <v>209.6</v>
-          </cell>
-          <cell r="D9">
-            <v>205.8</v>
-          </cell>
-          <cell r="E9">
-            <v>9.4</v>
-          </cell>
-          <cell r="F9">
-            <v>14.2</v>
-          </cell>
-          <cell r="G9">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H9">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I9">
-            <v>6.2</v>
-          </cell>
-          <cell r="J9">
-            <v>17.100000000000001</v>
-          </cell>
-          <cell r="K9">
-            <v>7</v>
-          </cell>
-          <cell r="L9">
-            <v>110</v>
-          </cell>
-          <cell r="M9">
-            <v>26</v>
-          </cell>
-          <cell r="N9">
-            <v>1.21</v>
-          </cell>
-          <cell r="O9">
-            <v>20.2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>203x203x71</v>
-          </cell>
-          <cell r="B10">
-            <v>71</v>
-          </cell>
-          <cell r="C10">
-            <v>215.8</v>
-          </cell>
-          <cell r="D10">
-            <v>206.4</v>
-          </cell>
-          <cell r="E10">
-            <v>10</v>
-          </cell>
-          <cell r="F10">
-            <v>17.3</v>
-          </cell>
-          <cell r="G10">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H10">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I10">
-            <v>5.09</v>
-          </cell>
-          <cell r="J10">
-            <v>16.100000000000001</v>
-          </cell>
-          <cell r="K10">
-            <v>7</v>
-          </cell>
-          <cell r="L10">
-            <v>110</v>
-          </cell>
-          <cell r="M10">
-            <v>28</v>
-          </cell>
-          <cell r="N10">
-            <v>1.22</v>
-          </cell>
-          <cell r="O10">
-            <v>17.2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>203x203x86</v>
-          </cell>
-          <cell r="B11">
-            <v>86.1</v>
-          </cell>
-          <cell r="C11">
-            <v>222.2</v>
-          </cell>
-          <cell r="D11">
-            <v>209.1</v>
-          </cell>
-          <cell r="E11">
-            <v>12.7</v>
-          </cell>
-          <cell r="F11">
-            <v>20.5</v>
-          </cell>
-          <cell r="G11">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H11">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I11">
-            <v>4.29</v>
-          </cell>
-          <cell r="J11">
-            <v>12.7</v>
-          </cell>
-          <cell r="K11">
-            <v>8</v>
-          </cell>
-          <cell r="L11">
-            <v>110</v>
-          </cell>
-          <cell r="M11">
-            <v>32</v>
-          </cell>
-          <cell r="N11">
-            <v>1.24</v>
-          </cell>
-          <cell r="O11">
-            <v>14.4</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>203x203x100+</v>
-          </cell>
-          <cell r="B12">
-            <v>99.6</v>
-          </cell>
-          <cell r="C12">
-            <v>228.6</v>
-          </cell>
-          <cell r="D12">
-            <v>210.3</v>
-          </cell>
-          <cell r="E12">
-            <v>14.5</v>
-          </cell>
-          <cell r="F12">
-            <v>23.7</v>
-          </cell>
-          <cell r="G12">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H12">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I12">
-            <v>3.7</v>
-          </cell>
-          <cell r="J12">
-            <v>11.1</v>
-          </cell>
-          <cell r="K12">
-            <v>9</v>
-          </cell>
-          <cell r="L12">
-            <v>108</v>
-          </cell>
-          <cell r="M12">
-            <v>34</v>
-          </cell>
-          <cell r="N12">
-            <v>1.25</v>
-          </cell>
-          <cell r="O12">
-            <v>12.6</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>203x203x113+</v>
-          </cell>
-          <cell r="B13">
-            <v>113.5</v>
-          </cell>
-          <cell r="C13">
-            <v>235</v>
-          </cell>
-          <cell r="D13">
-            <v>212.1</v>
-          </cell>
-          <cell r="E13">
-            <v>16.3</v>
-          </cell>
-          <cell r="F13">
-            <v>26.9</v>
-          </cell>
-          <cell r="G13">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H13">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I13">
-            <v>3.26</v>
-          </cell>
-          <cell r="J13">
-            <v>9.8699999999999992</v>
-          </cell>
-          <cell r="K13">
-            <v>10</v>
-          </cell>
-          <cell r="L13">
-            <v>108</v>
-          </cell>
-          <cell r="M13">
-            <v>38</v>
-          </cell>
-          <cell r="N13">
-            <v>1.27</v>
-          </cell>
-          <cell r="O13">
-            <v>11.2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>203x203x127+</v>
-          </cell>
-          <cell r="B14">
-            <v>127.5</v>
-          </cell>
-          <cell r="C14">
-            <v>241.4</v>
-          </cell>
-          <cell r="D14">
-            <v>213.9</v>
-          </cell>
-          <cell r="E14">
-            <v>18.100000000000001</v>
-          </cell>
-          <cell r="F14">
-            <v>30.1</v>
-          </cell>
-          <cell r="G14">
-            <v>10.199999999999999</v>
-          </cell>
-          <cell r="H14">
-            <v>160.80000000000001</v>
-          </cell>
-          <cell r="I14">
-            <v>2.91</v>
-          </cell>
-          <cell r="J14">
-            <v>8.8800000000000008</v>
-          </cell>
-          <cell r="K14">
-            <v>11</v>
-          </cell>
-          <cell r="L14">
-            <v>108</v>
-          </cell>
-          <cell r="M14">
-            <v>42</v>
-          </cell>
-          <cell r="N14">
-            <v>1.28</v>
-          </cell>
-          <cell r="O14">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>254x254x73</v>
-          </cell>
-          <cell r="B15">
-            <v>73.099999999999994</v>
-          </cell>
-          <cell r="C15">
-            <v>254.1</v>
-          </cell>
-          <cell r="D15">
-            <v>254.6</v>
-          </cell>
-          <cell r="E15">
-            <v>8.6</v>
-          </cell>
-          <cell r="F15">
-            <v>14.2</v>
-          </cell>
-          <cell r="G15">
-            <v>12.7</v>
-          </cell>
-          <cell r="H15">
-            <v>200.3</v>
-          </cell>
-          <cell r="I15">
-            <v>7.77</v>
-          </cell>
-          <cell r="J15">
-            <v>23.3</v>
-          </cell>
-          <cell r="K15">
-            <v>6</v>
-          </cell>
-          <cell r="L15">
-            <v>134</v>
-          </cell>
-          <cell r="M15">
-            <v>28</v>
-          </cell>
-          <cell r="N15">
-            <v>1.49</v>
-          </cell>
-          <cell r="O15">
-            <v>20.399999999999999</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>254x254x89</v>
-          </cell>
-          <cell r="B16">
-            <v>88.9</v>
-          </cell>
-          <cell r="C16">
-            <v>260.3</v>
-          </cell>
-          <cell r="D16">
-            <v>256.3</v>
-          </cell>
-          <cell r="E16">
-            <v>10.3</v>
-          </cell>
-          <cell r="F16">
-            <v>17.3</v>
-          </cell>
-          <cell r="G16">
-            <v>12.7</v>
-          </cell>
-          <cell r="H16">
-            <v>200.3</v>
-          </cell>
-          <cell r="I16">
-            <v>6.38</v>
-          </cell>
-          <cell r="J16">
-            <v>19.399999999999999</v>
-          </cell>
-          <cell r="K16">
-            <v>7</v>
-          </cell>
-          <cell r="L16">
-            <v>134</v>
-          </cell>
-          <cell r="M16">
-            <v>30</v>
-          </cell>
-          <cell r="N16">
-            <v>1.5</v>
-          </cell>
-          <cell r="O16">
-            <v>16.899999999999999</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>254x254x107</v>
-          </cell>
-          <cell r="B17">
-            <v>107.1</v>
-          </cell>
-          <cell r="C17">
-            <v>266.7</v>
-          </cell>
-          <cell r="D17">
-            <v>258.8</v>
-          </cell>
-          <cell r="E17">
-            <v>12.8</v>
-          </cell>
-          <cell r="F17">
-            <v>20.5</v>
-          </cell>
-          <cell r="G17">
-            <v>12.7</v>
-          </cell>
-          <cell r="H17">
-            <v>200.3</v>
-          </cell>
-          <cell r="I17">
-            <v>5.38</v>
-          </cell>
-          <cell r="J17">
-            <v>15.6</v>
-          </cell>
-          <cell r="K17">
-            <v>8</v>
-          </cell>
-          <cell r="L17">
-            <v>134</v>
-          </cell>
-          <cell r="M17">
-            <v>34</v>
-          </cell>
-          <cell r="N17">
-            <v>1.52</v>
-          </cell>
-          <cell r="O17">
-            <v>14.2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>254x254x132</v>
-          </cell>
-          <cell r="B18">
-            <v>132</v>
-          </cell>
-          <cell r="C18">
-            <v>276.3</v>
-          </cell>
-          <cell r="D18">
-            <v>261.3</v>
-          </cell>
-          <cell r="E18">
-            <v>15.3</v>
-          </cell>
-          <cell r="F18">
-            <v>25.3</v>
-          </cell>
-          <cell r="G18">
-            <v>12.7</v>
-          </cell>
-          <cell r="H18">
-            <v>200.3</v>
-          </cell>
-          <cell r="I18">
-            <v>4.3600000000000003</v>
-          </cell>
-          <cell r="J18">
-            <v>13.1</v>
-          </cell>
-          <cell r="K18">
-            <v>10</v>
-          </cell>
-          <cell r="L18">
-            <v>134</v>
-          </cell>
-          <cell r="M18">
-            <v>38</v>
-          </cell>
-          <cell r="N18">
-            <v>1.55</v>
-          </cell>
-          <cell r="O18">
-            <v>11.7</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>254x254x167</v>
-          </cell>
-          <cell r="B19">
-            <v>167.1</v>
-          </cell>
-          <cell r="C19">
-            <v>289.10000000000002</v>
-          </cell>
-          <cell r="D19">
-            <v>265.2</v>
-          </cell>
-          <cell r="E19">
-            <v>19.2</v>
-          </cell>
-          <cell r="F19">
-            <v>31.7</v>
-          </cell>
-          <cell r="G19">
-            <v>12.7</v>
-          </cell>
-          <cell r="H19">
-            <v>200.3</v>
-          </cell>
-          <cell r="I19">
-            <v>3.48</v>
-          </cell>
-          <cell r="J19">
-            <v>10.4</v>
-          </cell>
-          <cell r="K19">
-            <v>12</v>
-          </cell>
-          <cell r="L19">
-            <v>134</v>
-          </cell>
-          <cell r="M19">
-            <v>46</v>
-          </cell>
-          <cell r="N19">
-            <v>1.58</v>
-          </cell>
-          <cell r="O19">
-            <v>9.4600000000000009</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>305x305x97</v>
-          </cell>
-          <cell r="B20">
-            <v>96.9</v>
-          </cell>
-          <cell r="C20">
-            <v>307.89999999999998</v>
-          </cell>
-          <cell r="D20">
-            <v>305.3</v>
-          </cell>
-          <cell r="E20">
-            <v>9.9</v>
-          </cell>
-          <cell r="F20">
-            <v>15.4</v>
-          </cell>
-          <cell r="G20">
-            <v>15.2</v>
-          </cell>
-          <cell r="H20">
-            <v>246.7</v>
-          </cell>
-          <cell r="I20">
-            <v>8.6</v>
-          </cell>
-          <cell r="J20">
-            <v>24.9</v>
-          </cell>
-          <cell r="K20">
-            <v>7</v>
-          </cell>
-          <cell r="L20">
-            <v>158</v>
-          </cell>
-          <cell r="M20">
-            <v>32</v>
-          </cell>
-          <cell r="N20">
-            <v>1.79</v>
-          </cell>
-          <cell r="O20">
-            <v>18.5</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>305x305x118</v>
-          </cell>
-          <cell r="B21">
-            <v>117.9</v>
-          </cell>
-          <cell r="C21">
-            <v>314.5</v>
-          </cell>
-          <cell r="D21">
-            <v>307.39999999999998</v>
-          </cell>
-          <cell r="E21">
-            <v>12</v>
-          </cell>
-          <cell r="F21">
-            <v>18.7</v>
-          </cell>
-          <cell r="G21">
-            <v>15.2</v>
-          </cell>
-          <cell r="H21">
-            <v>246.7</v>
-          </cell>
-          <cell r="I21">
-            <v>7.09</v>
-          </cell>
-          <cell r="J21">
-            <v>20.6</v>
-          </cell>
-          <cell r="K21">
-            <v>8</v>
-          </cell>
-          <cell r="L21">
-            <v>158</v>
-          </cell>
-          <cell r="M21">
-            <v>34</v>
-          </cell>
-          <cell r="N21">
-            <v>1.81</v>
-          </cell>
-          <cell r="O21">
-            <v>15.4</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>305x305x137</v>
-          </cell>
-          <cell r="B22">
-            <v>136.9</v>
-          </cell>
-          <cell r="C22">
-            <v>320.5</v>
-          </cell>
-          <cell r="D22">
-            <v>309.2</v>
-          </cell>
-          <cell r="E22">
-            <v>13.8</v>
-          </cell>
-          <cell r="F22">
-            <v>21.7</v>
-          </cell>
-          <cell r="G22">
-            <v>15.2</v>
-          </cell>
-          <cell r="H22">
-            <v>246.7</v>
-          </cell>
-          <cell r="I22">
-            <v>6.11</v>
-          </cell>
-          <cell r="J22">
-            <v>17.899999999999999</v>
-          </cell>
-          <cell r="K22">
-            <v>9</v>
-          </cell>
-          <cell r="L22">
-            <v>158</v>
-          </cell>
-          <cell r="M22">
-            <v>38</v>
-          </cell>
-          <cell r="N22">
-            <v>1.82</v>
-          </cell>
-          <cell r="O22">
-            <v>13.3</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>305x305x158</v>
-          </cell>
-          <cell r="B23">
-            <v>158.1</v>
-          </cell>
-          <cell r="C23">
-            <v>327.10000000000002</v>
-          </cell>
-          <cell r="D23">
-            <v>311.2</v>
-          </cell>
-          <cell r="E23">
-            <v>15.8</v>
-          </cell>
-          <cell r="F23">
-            <v>25</v>
-          </cell>
-          <cell r="G23">
-            <v>15.2</v>
-          </cell>
-          <cell r="H23">
-            <v>246.7</v>
-          </cell>
-          <cell r="I23">
-            <v>5.3</v>
-          </cell>
-          <cell r="J23">
-            <v>15.6</v>
-          </cell>
-          <cell r="K23">
-            <v>10</v>
-          </cell>
-          <cell r="L23">
-            <v>158</v>
-          </cell>
-          <cell r="M23">
-            <v>42</v>
-          </cell>
-          <cell r="N23">
-            <v>1.84</v>
-          </cell>
-          <cell r="O23">
-            <v>11.6</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>305x305x198</v>
-          </cell>
-          <cell r="B24">
-            <v>198.1</v>
-          </cell>
-          <cell r="C24">
-            <v>339.9</v>
-          </cell>
-          <cell r="D24">
-            <v>314.5</v>
-          </cell>
-          <cell r="E24">
-            <v>19.100000000000001</v>
-          </cell>
-          <cell r="F24">
-            <v>31.4</v>
-          </cell>
-          <cell r="G24">
-            <v>15.2</v>
-          </cell>
-          <cell r="H24">
-            <v>246.7</v>
-          </cell>
-          <cell r="I24">
-            <v>4.22</v>
-          </cell>
-          <cell r="J24">
-            <v>12.9</v>
-          </cell>
-          <cell r="K24">
-            <v>12</v>
-          </cell>
-          <cell r="L24">
-            <v>158</v>
-          </cell>
-          <cell r="M24">
-            <v>48</v>
-          </cell>
-          <cell r="N24">
-            <v>1.87</v>
-          </cell>
-          <cell r="O24">
-            <v>9.44</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>305x305x240</v>
-          </cell>
-          <cell r="B25">
-            <v>240</v>
-          </cell>
-          <cell r="C25">
-            <v>352.5</v>
-          </cell>
-          <cell r="D25">
-            <v>318.39999999999998</v>
-          </cell>
-          <cell r="E25">
-            <v>23</v>
-          </cell>
-          <cell r="F25">
-            <v>37.700000000000003</v>
-          </cell>
-          <cell r="G25">
-            <v>15.2</v>
-          </cell>
-          <cell r="H25">
-            <v>246.7</v>
-          </cell>
-          <cell r="I25">
-            <v>3.51</v>
-          </cell>
-          <cell r="J25">
-            <v>10.7</v>
-          </cell>
-          <cell r="K25">
-            <v>14</v>
-          </cell>
-          <cell r="L25">
-            <v>158</v>
-          </cell>
-          <cell r="M25">
-            <v>54</v>
-          </cell>
-          <cell r="N25">
-            <v>1.91</v>
-          </cell>
-          <cell r="O25">
-            <v>7.96</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>305x305x283</v>
-          </cell>
-          <cell r="B26">
-            <v>282.89999999999998</v>
-          </cell>
-          <cell r="C26">
-            <v>365.3</v>
-          </cell>
-          <cell r="D26">
-            <v>322.2</v>
-          </cell>
-          <cell r="E26">
-            <v>26.8</v>
-          </cell>
-          <cell r="F26">
-            <v>44.1</v>
-          </cell>
-          <cell r="G26">
-            <v>15.2</v>
-          </cell>
-          <cell r="H26">
-            <v>246.7</v>
-          </cell>
-          <cell r="I26">
-            <v>3</v>
-          </cell>
-          <cell r="J26">
-            <v>9.2100000000000009</v>
-          </cell>
-          <cell r="K26">
-            <v>15</v>
-          </cell>
-          <cell r="L26">
-            <v>158</v>
-          </cell>
-          <cell r="M26">
-            <v>60</v>
-          </cell>
-          <cell r="N26">
-            <v>1.94</v>
-          </cell>
-          <cell r="O26">
-            <v>6.86</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>356x368x129</v>
-          </cell>
-          <cell r="B27">
-            <v>129</v>
-          </cell>
-          <cell r="C27">
-            <v>355.6</v>
-          </cell>
-          <cell r="D27">
-            <v>368.6</v>
-          </cell>
-          <cell r="E27">
-            <v>10.4</v>
-          </cell>
-          <cell r="F27">
-            <v>17.5</v>
-          </cell>
-          <cell r="G27">
-            <v>15.2</v>
-          </cell>
-          <cell r="H27">
-            <v>290.2</v>
-          </cell>
-          <cell r="I27">
-            <v>9.4</v>
-          </cell>
-          <cell r="J27">
-            <v>27.9</v>
-          </cell>
-          <cell r="K27">
-            <v>7</v>
-          </cell>
-          <cell r="L27">
-            <v>190</v>
-          </cell>
-          <cell r="M27">
-            <v>34</v>
-          </cell>
-          <cell r="N27">
-            <v>2.14</v>
-          </cell>
-          <cell r="O27">
-            <v>16.600000000000001</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>356x368x153</v>
-          </cell>
-          <cell r="B28">
-            <v>152.9</v>
-          </cell>
-          <cell r="C28">
-            <v>362</v>
-          </cell>
-          <cell r="D28">
-            <v>370.5</v>
-          </cell>
-          <cell r="E28">
-            <v>12.3</v>
-          </cell>
-          <cell r="F28">
-            <v>20.7</v>
-          </cell>
-          <cell r="G28">
-            <v>15.2</v>
-          </cell>
-          <cell r="H28">
-            <v>290.2</v>
-          </cell>
-          <cell r="I28">
-            <v>7.92</v>
-          </cell>
-          <cell r="J28">
-            <v>23.6</v>
-          </cell>
-          <cell r="K28">
-            <v>8</v>
-          </cell>
-          <cell r="L28">
-            <v>190</v>
-          </cell>
-          <cell r="M28">
-            <v>36</v>
-          </cell>
-          <cell r="N28">
-            <v>2.16</v>
-          </cell>
-          <cell r="O28">
-            <v>14.1</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>356x368x177</v>
-          </cell>
-          <cell r="B29">
-            <v>177</v>
-          </cell>
-          <cell r="C29">
-            <v>368.2</v>
-          </cell>
-          <cell r="D29">
-            <v>372.6</v>
-          </cell>
-          <cell r="E29">
-            <v>14.4</v>
-          </cell>
-          <cell r="F29">
-            <v>23.8</v>
-          </cell>
-          <cell r="G29">
-            <v>15.2</v>
-          </cell>
-          <cell r="H29">
-            <v>290.2</v>
-          </cell>
-          <cell r="I29">
-            <v>6.89</v>
-          </cell>
-          <cell r="J29">
-            <v>20.2</v>
-          </cell>
-          <cell r="K29">
-            <v>9</v>
-          </cell>
-          <cell r="L29">
-            <v>190</v>
-          </cell>
-          <cell r="M29">
-            <v>40</v>
-          </cell>
-          <cell r="N29">
-            <v>2.17</v>
-          </cell>
-          <cell r="O29">
-            <v>12.3</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>356x368x202</v>
-          </cell>
-          <cell r="B30">
-            <v>201.9</v>
-          </cell>
-          <cell r="C30">
-            <v>374.6</v>
-          </cell>
-          <cell r="D30">
-            <v>374.7</v>
-          </cell>
-          <cell r="E30">
-            <v>16.5</v>
-          </cell>
-          <cell r="F30">
-            <v>27</v>
-          </cell>
-          <cell r="G30">
-            <v>15.2</v>
-          </cell>
-          <cell r="H30">
-            <v>290.2</v>
-          </cell>
-          <cell r="I30">
-            <v>6.07</v>
-          </cell>
-          <cell r="J30">
-            <v>17.600000000000001</v>
-          </cell>
-          <cell r="K30">
-            <v>10</v>
-          </cell>
-          <cell r="L30">
-            <v>190</v>
-          </cell>
-          <cell r="M30">
-            <v>44</v>
-          </cell>
-          <cell r="N30">
-            <v>2.19</v>
-          </cell>
-          <cell r="O30">
-            <v>10.8</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>356x406x235</v>
-          </cell>
-          <cell r="B31">
-            <v>235.1</v>
-          </cell>
-          <cell r="C31">
-            <v>381</v>
-          </cell>
-          <cell r="D31">
-            <v>394.8</v>
-          </cell>
-          <cell r="E31">
-            <v>18.399999999999999</v>
-          </cell>
-          <cell r="F31">
-            <v>30.2</v>
-          </cell>
-          <cell r="G31">
-            <v>15.2</v>
-          </cell>
-          <cell r="H31">
-            <v>290.2</v>
-          </cell>
-          <cell r="I31">
-            <v>5.73</v>
-          </cell>
-          <cell r="J31">
-            <v>15.8</v>
-          </cell>
-          <cell r="K31">
-            <v>11</v>
-          </cell>
-          <cell r="L31">
-            <v>200</v>
-          </cell>
-          <cell r="M31">
-            <v>46</v>
-          </cell>
-          <cell r="N31">
-            <v>2.2799999999999998</v>
-          </cell>
-          <cell r="O31">
-            <v>9.6999999999999993</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>356x406x287</v>
-          </cell>
-          <cell r="B32">
-            <v>287.10000000000002</v>
-          </cell>
-          <cell r="C32">
-            <v>393.6</v>
-          </cell>
-          <cell r="D32">
-            <v>399</v>
-          </cell>
-          <cell r="E32">
-            <v>22.6</v>
-          </cell>
-          <cell r="F32">
-            <v>36.5</v>
-          </cell>
-          <cell r="G32">
-            <v>15.2</v>
-          </cell>
-          <cell r="H32">
-            <v>290.2</v>
-          </cell>
-          <cell r="I32">
-            <v>4.74</v>
-          </cell>
-          <cell r="J32">
-            <v>12.8</v>
-          </cell>
-          <cell r="K32">
-            <v>13</v>
-          </cell>
-          <cell r="L32">
-            <v>200</v>
-          </cell>
-          <cell r="M32">
-            <v>52</v>
-          </cell>
-          <cell r="N32">
-            <v>2.31</v>
-          </cell>
-          <cell r="O32">
-            <v>8.0500000000000007</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>356x406x340</v>
-          </cell>
-          <cell r="B33">
-            <v>339.9</v>
-          </cell>
-          <cell r="C33">
-            <v>406.4</v>
-          </cell>
-          <cell r="D33">
-            <v>403</v>
-          </cell>
-          <cell r="E33">
-            <v>26.6</v>
-          </cell>
-          <cell r="F33">
-            <v>42.9</v>
-          </cell>
-          <cell r="G33">
-            <v>15.2</v>
-          </cell>
-          <cell r="H33">
-            <v>290.2</v>
-          </cell>
-          <cell r="I33">
-            <v>4.03</v>
-          </cell>
-          <cell r="J33">
-            <v>10.9</v>
-          </cell>
-          <cell r="K33">
-            <v>15</v>
-          </cell>
-          <cell r="L33">
-            <v>200</v>
-          </cell>
-          <cell r="M33">
-            <v>60</v>
-          </cell>
-          <cell r="N33">
-            <v>2.35</v>
-          </cell>
-          <cell r="O33">
-            <v>6.91</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>356x406x393</v>
-          </cell>
-          <cell r="B34">
-            <v>393</v>
-          </cell>
-          <cell r="C34">
-            <v>419</v>
-          </cell>
-          <cell r="D34">
-            <v>407</v>
-          </cell>
-          <cell r="E34">
-            <v>30.6</v>
-          </cell>
-          <cell r="F34">
-            <v>49.2</v>
-          </cell>
-          <cell r="G34">
-            <v>15.2</v>
-          </cell>
-          <cell r="H34">
-            <v>290.2</v>
-          </cell>
-          <cell r="I34">
-            <v>3.52</v>
-          </cell>
-          <cell r="J34">
-            <v>9.48</v>
-          </cell>
-          <cell r="K34">
-            <v>17</v>
-          </cell>
-          <cell r="L34">
-            <v>200</v>
-          </cell>
-          <cell r="M34">
-            <v>66</v>
-          </cell>
-          <cell r="N34">
-            <v>2.38</v>
-          </cell>
-          <cell r="O34">
-            <v>6.06</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>356x406x467</v>
-          </cell>
-          <cell r="B35">
-            <v>467</v>
-          </cell>
-          <cell r="C35">
-            <v>436.6</v>
-          </cell>
-          <cell r="D35">
-            <v>412.2</v>
-          </cell>
-          <cell r="E35">
-            <v>35.799999999999997</v>
-          </cell>
-          <cell r="F35">
-            <v>58</v>
-          </cell>
-          <cell r="G35">
-            <v>15.2</v>
-          </cell>
-          <cell r="H35">
-            <v>290.2</v>
-          </cell>
-          <cell r="I35">
-            <v>2.98</v>
-          </cell>
-          <cell r="J35">
-            <v>8.11</v>
-          </cell>
-          <cell r="K35">
-            <v>20</v>
-          </cell>
-          <cell r="L35">
-            <v>200</v>
-          </cell>
-          <cell r="M35">
-            <v>74</v>
-          </cell>
-          <cell r="N35">
-            <v>2.42</v>
-          </cell>
-          <cell r="O35">
-            <v>5.18</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>356x406x551</v>
-          </cell>
-          <cell r="B36">
-            <v>551</v>
-          </cell>
-          <cell r="C36">
-            <v>455.6</v>
-          </cell>
-          <cell r="D36">
-            <v>418.5</v>
-          </cell>
-          <cell r="E36">
-            <v>42.1</v>
-          </cell>
-          <cell r="F36">
-            <v>67.5</v>
-          </cell>
-          <cell r="G36">
-            <v>15.2</v>
-          </cell>
-          <cell r="H36">
-            <v>290.2</v>
-          </cell>
-          <cell r="I36">
-            <v>2.56</v>
-          </cell>
-          <cell r="J36">
-            <v>6.89</v>
-          </cell>
-          <cell r="K36">
-            <v>23</v>
-          </cell>
-          <cell r="L36">
-            <v>200</v>
-          </cell>
-          <cell r="M36">
-            <v>84</v>
-          </cell>
-          <cell r="N36">
-            <v>2.4700000000000002</v>
-          </cell>
-          <cell r="O36">
-            <v>4.4800000000000004</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>356x406x634</v>
-          </cell>
-          <cell r="B37">
-            <v>633.9</v>
-          </cell>
-          <cell r="C37">
-            <v>474.6</v>
-          </cell>
-          <cell r="D37">
-            <v>424</v>
-          </cell>
-          <cell r="E37">
-            <v>47.6</v>
-          </cell>
-          <cell r="F37">
-            <v>77</v>
-          </cell>
-          <cell r="G37">
-            <v>15.2</v>
-          </cell>
-          <cell r="H37">
-            <v>290.2</v>
-          </cell>
-          <cell r="I37">
-            <v>2.25</v>
-          </cell>
-          <cell r="J37">
-            <v>6.1</v>
-          </cell>
-          <cell r="K37">
-            <v>26</v>
-          </cell>
-          <cell r="L37">
-            <v>200</v>
-          </cell>
-          <cell r="M37">
-            <v>94</v>
-          </cell>
-          <cell r="N37">
-            <v>2.52</v>
-          </cell>
-          <cell r="O37">
-            <v>3.98</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2347,19 +566,15 @@
         <v>2920</v>
       </c>
       <c r="O2">
-        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>5.8</v>
       </c>
       <c r="P2">
-        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>152.4</v>
       </c>
       <c r="Q2">
-        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>6.8</v>
       </c>
       <c r="S2">
-        <f>VLOOKUP(A2,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>152.19999999999999</v>
       </c>
     </row>
@@ -2407,19 +622,15 @@
         <v>3829.9999999999995</v>
       </c>
       <c r="O3">
-        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>6.5</v>
       </c>
       <c r="P3">
-        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>157.6</v>
       </c>
       <c r="Q3">
-        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>9.4</v>
       </c>
       <c r="S3">
-        <f>VLOOKUP(A3,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>152.9</v>
       </c>
     </row>
@@ -2467,19 +678,15 @@
         <v>4710</v>
       </c>
       <c r="O4">
-        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>8</v>
       </c>
       <c r="P4">
-        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>161.80000000000001</v>
       </c>
       <c r="Q4">
-        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>11.5</v>
       </c>
       <c r="S4">
-        <f>VLOOKUP(A4,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>154.4</v>
       </c>
     </row>
@@ -2527,19 +734,15 @@
         <v>5610</v>
       </c>
       <c r="O5">
-        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>9.5</v>
       </c>
       <c r="P5">
-        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>166</v>
       </c>
       <c r="Q5">
-        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>13.6</v>
       </c>
       <c r="S5">
-        <f>VLOOKUP(A5,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>155.9</v>
       </c>
     </row>
@@ -2587,19 +790,15 @@
         <v>5870</v>
       </c>
       <c r="O6">
-        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>7.2</v>
       </c>
       <c r="P6">
-        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>203.2</v>
       </c>
       <c r="Q6">
-        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>11</v>
       </c>
       <c r="S6">
-        <f>VLOOKUP(A6,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>203.6</v>
       </c>
     </row>
@@ -2647,19 +846,15 @@
         <v>6520</v>
       </c>
       <c r="O7">
-        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>11</v>
       </c>
       <c r="P7">
-        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>170.2</v>
       </c>
       <c r="Q7">
-        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>15.7</v>
       </c>
       <c r="S7">
-        <f>VLOOKUP(A7,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>157.4</v>
       </c>
     </row>
@@ -2707,19 +902,15 @@
         <v>6630</v>
       </c>
       <c r="O8">
-        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>7.9</v>
       </c>
       <c r="P8">
-        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>206.2</v>
       </c>
       <c r="Q8">
-        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>12.5</v>
       </c>
       <c r="S8">
-        <f>VLOOKUP(A8,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>204.3</v>
       </c>
     </row>
@@ -2767,19 +958,15 @@
         <v>7640.0000000000009</v>
       </c>
       <c r="O9">
-        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>9.4</v>
       </c>
       <c r="P9">
-        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>209.6</v>
       </c>
       <c r="Q9">
-        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>14.2</v>
       </c>
       <c r="S9">
-        <f>VLOOKUP(A9,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>205.8</v>
       </c>
     </row>
@@ -2827,19 +1014,15 @@
         <v>9040</v>
       </c>
       <c r="O10">
-        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>10</v>
       </c>
       <c r="P10">
-        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>215.8</v>
       </c>
       <c r="Q10">
-        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>17.3</v>
       </c>
       <c r="S10">
-        <f>VLOOKUP(A10,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>206.4</v>
       </c>
     </row>
@@ -2887,19 +1070,15 @@
         <v>9310</v>
       </c>
       <c r="O11">
-        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>8.6</v>
       </c>
       <c r="P11">
-        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>254.1</v>
       </c>
       <c r="Q11">
-        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>14.2</v>
       </c>
       <c r="S11">
-        <f>VLOOKUP(A11,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>254.6</v>
       </c>
     </row>
@@ -2947,19 +1126,15 @@
         <v>11000</v>
       </c>
       <c r="O12">
-        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>12.7</v>
       </c>
       <c r="P12">
-        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>222.2</v>
       </c>
       <c r="Q12">
-        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>20.5</v>
       </c>
       <c r="S12">
-        <f>VLOOKUP(A12,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>209.1</v>
       </c>
     </row>
@@ -3007,19 +1182,15 @@
         <v>11300</v>
       </c>
       <c r="O13">
-        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>10.3</v>
       </c>
       <c r="P13">
-        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>260.3</v>
       </c>
       <c r="Q13">
-        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>17.3</v>
       </c>
       <c r="S13">
-        <f>VLOOKUP(A13,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>256.3</v>
       </c>
     </row>
@@ -3067,19 +1238,15 @@
         <v>12300</v>
       </c>
       <c r="O14">
-        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>9.9</v>
       </c>
       <c r="P14">
-        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>307.89999999999998</v>
       </c>
       <c r="Q14">
-        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>15.4</v>
       </c>
       <c r="S14">
-        <f>VLOOKUP(A14,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>305.3</v>
       </c>
     </row>
@@ -3127,19 +1294,15 @@
         <v>12700</v>
       </c>
       <c r="O15">
-        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>14.5</v>
       </c>
       <c r="P15">
-        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>228.6</v>
       </c>
       <c r="Q15">
-        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>23.7</v>
       </c>
       <c r="S15">
-        <f>VLOOKUP(A15,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>210.3</v>
       </c>
     </row>
@@ -3187,19 +1350,15 @@
         <v>13600</v>
       </c>
       <c r="O16">
-        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>12.8</v>
       </c>
       <c r="P16">
-        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>266.7</v>
       </c>
       <c r="Q16">
-        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>20.5</v>
       </c>
       <c r="S16">
-        <f>VLOOKUP(A16,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>258.8</v>
       </c>
     </row>
@@ -3247,19 +1406,15 @@
         <v>14500</v>
       </c>
       <c r="O17">
-        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>16.3</v>
       </c>
       <c r="P17">
-        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>235</v>
       </c>
       <c r="Q17">
-        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>26.9</v>
       </c>
       <c r="S17">
-        <f>VLOOKUP(A17,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>212.1</v>
       </c>
     </row>
@@ -3307,19 +1462,15 @@
         <v>15000</v>
       </c>
       <c r="O18">
-        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>12</v>
       </c>
       <c r="P18">
-        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>314.5</v>
       </c>
       <c r="Q18">
-        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>18.7</v>
       </c>
       <c r="S18">
-        <f>VLOOKUP(A18,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>307.39999999999998</v>
       </c>
     </row>
@@ -3367,19 +1518,15 @@
         <v>16200</v>
       </c>
       <c r="O19">
-        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>18.100000000000001</v>
       </c>
       <c r="P19">
-        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>241.4</v>
       </c>
       <c r="Q19">
-        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>30.1</v>
       </c>
       <c r="S19">
-        <f>VLOOKUP(A19,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>213.9</v>
       </c>
     </row>
@@ -3427,19 +1574,15 @@
         <v>16400</v>
       </c>
       <c r="O20">
-        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>10.4</v>
       </c>
       <c r="P20">
-        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>355.6</v>
       </c>
       <c r="Q20">
-        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>17.5</v>
       </c>
       <c r="S20">
-        <f>VLOOKUP(A20,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>368.6</v>
       </c>
     </row>
@@ -3487,19 +1630,15 @@
         <v>16800</v>
       </c>
       <c r="O21">
-        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>15.3</v>
       </c>
       <c r="P21">
-        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>276.3</v>
       </c>
       <c r="Q21">
-        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>25.3</v>
       </c>
       <c r="S21">
-        <f>VLOOKUP(A21,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>261.3</v>
       </c>
     </row>
@@ -3547,19 +1686,15 @@
         <v>17400</v>
       </c>
       <c r="O22">
-        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>13.8</v>
       </c>
       <c r="P22">
-        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>320.5</v>
       </c>
       <c r="Q22">
-        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>21.7</v>
       </c>
       <c r="S22">
-        <f>VLOOKUP(A22,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>309.2</v>
       </c>
     </row>
@@ -3607,19 +1742,15 @@
         <v>19500</v>
       </c>
       <c r="O23">
-        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>12.3</v>
       </c>
       <c r="P23">
-        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>362</v>
       </c>
       <c r="Q23">
-        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>20.7</v>
       </c>
       <c r="S23">
-        <f>VLOOKUP(A23,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>370.5</v>
       </c>
     </row>
@@ -3667,19 +1798,15 @@
         <v>20100</v>
       </c>
       <c r="O24">
-        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>15.8</v>
       </c>
       <c r="P24">
-        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>327.10000000000002</v>
       </c>
       <c r="Q24">
-        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>25</v>
       </c>
       <c r="S24">
-        <f>VLOOKUP(A24,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>311.2</v>
       </c>
     </row>
@@ -3727,19 +1854,15 @@
         <v>21300</v>
       </c>
       <c r="O25">
-        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>19.2</v>
       </c>
       <c r="P25">
-        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>289.10000000000002</v>
       </c>
       <c r="Q25">
-        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>31.7</v>
       </c>
       <c r="S25">
-        <f>VLOOKUP(A25,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>265.2</v>
       </c>
     </row>
@@ -3787,19 +1910,15 @@
         <v>22600</v>
       </c>
       <c r="O26">
-        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>14.4</v>
       </c>
       <c r="P26">
-        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>368.2</v>
       </c>
       <c r="Q26">
-        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>23.8</v>
       </c>
       <c r="S26">
-        <f>VLOOKUP(A26,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>372.6</v>
       </c>
     </row>
@@ -3847,19 +1966,15 @@
         <v>25200</v>
       </c>
       <c r="O27">
-        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>19.100000000000001</v>
       </c>
       <c r="P27">
-        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>339.9</v>
       </c>
       <c r="Q27">
-        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>31.4</v>
       </c>
       <c r="S27">
-        <f>VLOOKUP(A27,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>314.5</v>
       </c>
     </row>
@@ -3907,19 +2022,15 @@
         <v>25700</v>
       </c>
       <c r="O28">
-        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>16.5</v>
       </c>
       <c r="P28">
-        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>374.6</v>
       </c>
       <c r="Q28">
-        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>27</v>
       </c>
       <c r="S28">
-        <f>VLOOKUP(A28,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>374.7</v>
       </c>
     </row>
@@ -3967,19 +2078,15 @@
         <v>29900</v>
       </c>
       <c r="O29">
-        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>18.399999999999999</v>
       </c>
       <c r="P29">
-        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>381</v>
       </c>
       <c r="Q29">
-        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>30.2</v>
       </c>
       <c r="S29">
-        <f>VLOOKUP(A29,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>394.8</v>
       </c>
     </row>
@@ -4027,19 +2134,15 @@
         <v>30600</v>
       </c>
       <c r="O30">
-        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>23</v>
       </c>
       <c r="P30">
-        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>352.5</v>
       </c>
       <c r="Q30">
-        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>37.700000000000003</v>
       </c>
       <c r="S30">
-        <f>VLOOKUP(A30,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>318.39999999999998</v>
       </c>
     </row>
@@ -4087,19 +2190,15 @@
         <v>36000</v>
       </c>
       <c r="O31">
-        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>26.8</v>
       </c>
       <c r="P31">
-        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>365.3</v>
       </c>
       <c r="Q31">
-        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>44.1</v>
       </c>
       <c r="S31">
-        <f>VLOOKUP(A31,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>322.2</v>
       </c>
     </row>
@@ -4147,19 +2246,15 @@
         <v>36600</v>
       </c>
       <c r="O32">
-        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>22.6</v>
       </c>
       <c r="P32">
-        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>393.6</v>
       </c>
       <c r="Q32">
-        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>36.5</v>
       </c>
       <c r="S32">
-        <f>VLOOKUP(A32,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>399</v>
       </c>
     </row>
@@ -4207,19 +2302,15 @@
         <v>43300</v>
       </c>
       <c r="O33">
-        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>26.6</v>
       </c>
       <c r="P33">
-        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>406.4</v>
       </c>
       <c r="Q33">
-        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>42.9</v>
       </c>
       <c r="S33">
-        <f>VLOOKUP(A33,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>403</v>
       </c>
     </row>
@@ -4267,19 +2358,15 @@
         <v>50100</v>
       </c>
       <c r="O34">
-        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>30.6</v>
       </c>
       <c r="P34">
-        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>419</v>
       </c>
       <c r="Q34">
-        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>49.2</v>
       </c>
       <c r="S34">
-        <f>VLOOKUP(A34,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>407</v>
       </c>
     </row>
@@ -4327,19 +2414,15 @@
         <v>59500</v>
       </c>
       <c r="O35">
-        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>35.799999999999997</v>
       </c>
       <c r="P35">
-        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>436.6</v>
       </c>
       <c r="Q35">
-        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>58</v>
       </c>
       <c r="S35">
-        <f>VLOOKUP(A35,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>412.2</v>
       </c>
     </row>
@@ -4387,19 +2470,15 @@
         <v>70200</v>
       </c>
       <c r="O36">
-        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>42.1</v>
       </c>
       <c r="P36">
-        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>455.6</v>
       </c>
       <c r="Q36">
-        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>67.5</v>
       </c>
       <c r="S36">
-        <f>VLOOKUP(A36,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>418.5</v>
       </c>
     </row>
@@ -4447,19 +2526,15 @@
         <v>80800</v>
       </c>
       <c r="O37">
-        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,5,FALSE)</f>
         <v>47.6</v>
       </c>
       <c r="P37">
-        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,3,FALSE)</f>
         <v>474.6</v>
       </c>
       <c r="Q37">
-        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,6,FALSE)</f>
         <v>77</v>
       </c>
       <c r="S37">
-        <f>VLOOKUP(A37,'[1]Structural Steel Section Proper'!$A$1:$O$37,4,FALSE)</f>
         <v>424</v>
       </c>
     </row>
